--- a/ECB_skewness.xlsx
+++ b/ECB_skewness.xlsx
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -130,13 +130,13 @@
         <v>0.47890686988830566</v>
       </c>
       <c r="C5" s="2">
-        <v>0.37072709202766418</v>
+        <v>0.36112922430038452</v>
       </c>
       <c r="D5" s="2">
         <v>0.60682821273803711</v>
       </c>
       <c r="E5" s="2">
-        <v>0.56078648567199707</v>
+        <v>0.5575060248374939</v>
       </c>
     </row>
     <row r="6">
@@ -147,13 +147,13 @@
         <v>0.5860331654548645</v>
       </c>
       <c r="C6" s="2">
-        <v>0.52606886625289917</v>
+        <v>0.51956474781036377</v>
       </c>
       <c r="D6" s="2">
         <v>0.58285558223724365</v>
       </c>
       <c r="E6" s="2">
-        <v>0.52861630916595459</v>
+        <v>0.52695721387863159</v>
       </c>
     </row>
     <row r="7">
@@ -164,13 +164,13 @@
         <v>0.80940514802932739</v>
       </c>
       <c r="C7" s="2">
-        <v>0.73801320791244507</v>
+        <v>0.73125278949737549</v>
       </c>
       <c r="D7" s="2">
         <v>0.62259155511856079</v>
       </c>
       <c r="E7" s="2">
-        <v>0.56516802310943604</v>
+        <v>0.562874436378479</v>
       </c>
     </row>
     <row r="8">
@@ -181,13 +181,13 @@
         <v>0.43972894549369812</v>
       </c>
       <c r="C8" s="2">
-        <v>0.41535386443138123</v>
+        <v>0.4131368100643158</v>
       </c>
       <c r="D8" s="2">
         <v>0.59996819496154785</v>
       </c>
       <c r="E8" s="2">
-        <v>0.54142719507217407</v>
+        <v>0.53927195072174072</v>
       </c>
     </row>
     <row r="9">
@@ -198,13 +198,13 @@
         <v>0.72006678581237793</v>
       </c>
       <c r="C9" s="2">
-        <v>0.75376933813095093</v>
+        <v>0.76244664192199707</v>
       </c>
       <c r="D9" s="2">
         <v>0.6180424690246582</v>
       </c>
       <c r="E9" s="2">
-        <v>0.56387245655059814</v>
+        <v>0.56135892868041992</v>
       </c>
     </row>
     <row r="10">
@@ -215,13 +215,13 @@
         <v>0.46299266815185547</v>
       </c>
       <c r="C10" s="2">
-        <v>0.36776545643806458</v>
+        <v>0.37421295046806335</v>
       </c>
       <c r="D10" s="2">
         <v>0.62297284603118896</v>
       </c>
       <c r="E10" s="2">
-        <v>0.57307511568069458</v>
+        <v>0.57097470760345459</v>
       </c>
     </row>
     <row r="11">
@@ -232,13 +232,13 @@
         <v>0.86100733280181885</v>
       </c>
       <c r="C11" s="2">
-        <v>0.78447830677032471</v>
+        <v>0.77837800979614258</v>
       </c>
       <c r="D11" s="2">
         <v>0.63974106311798096</v>
       </c>
       <c r="E11" s="2">
-        <v>0.59626471996307373</v>
+        <v>0.59410160779953003</v>
       </c>
     </row>
     <row r="12">
@@ -249,13 +249,13 @@
         <v>0.44160452485084534</v>
       </c>
       <c r="C12" s="2">
-        <v>0.37524142861366272</v>
+        <v>0.37405461072921753</v>
       </c>
       <c r="D12" s="2">
         <v>0.57559704780578613</v>
       </c>
       <c r="E12" s="2">
-        <v>0.53597396612167358</v>
+        <v>0.53431284427642822</v>
       </c>
     </row>
     <row r="13">
@@ -266,13 +266,13 @@
         <v>0.76263660192489624</v>
       </c>
       <c r="C13" s="2">
-        <v>0.74343442916870117</v>
+        <v>0.73805445432662964</v>
       </c>
       <c r="D13" s="2">
         <v>0.54548430442810059</v>
       </c>
       <c r="E13" s="2">
-        <v>0.515350341796875</v>
+        <v>0.51403790712356567</v>
       </c>
     </row>
     <row r="14">
@@ -283,13 +283,13 @@
         <v>0.52328032255172729</v>
       </c>
       <c r="C14" s="2">
-        <v>0.45355129241943359</v>
+        <v>0.44767138361930847</v>
       </c>
       <c r="D14" s="2">
         <v>0.46770617365837097</v>
       </c>
       <c r="E14" s="2">
-        <v>0.42931428551673889</v>
+        <v>0.42708951234817505</v>
       </c>
     </row>
     <row r="15">
@@ -300,13 +300,13 @@
         <v>0.73694723844528198</v>
       </c>
       <c r="C15" s="2">
-        <v>0.73477494716644287</v>
+        <v>0.72770684957504272</v>
       </c>
       <c r="D15" s="2">
         <v>0.52602195739746094</v>
       </c>
       <c r="E15" s="2">
-        <v>0.49583402276039124</v>
+        <v>0.49184823036193848</v>
       </c>
     </row>
     <row r="16">
@@ -317,13 +317,13 @@
         <v>0.23210926353931427</v>
       </c>
       <c r="C16" s="2">
-        <v>0.19539661705493927</v>
+        <v>0.19315378367900848</v>
       </c>
       <c r="D16" s="2">
         <v>0.52616488933563232</v>
       </c>
       <c r="E16" s="2">
-        <v>0.49776607751846313</v>
+        <v>0.49321529269218445</v>
       </c>
     </row>
     <row r="17">
@@ -334,13 +334,13 @@
         <v>0.168714240193367</v>
       </c>
       <c r="C17" s="2">
-        <v>0.22974132001399994</v>
+        <v>0.23066255450248718</v>
       </c>
       <c r="D17" s="2">
         <v>0.56414449214935303</v>
       </c>
       <c r="E17" s="2">
-        <v>0.53470790386199951</v>
+        <v>0.52928394079208374</v>
       </c>
     </row>
     <row r="18">
@@ -351,13 +351,13 @@
         <v>0.020063307136297226</v>
       </c>
       <c r="C18" s="2">
-        <v>-0.020555285736918449</v>
+        <v>-0.020088881254196167</v>
       </c>
       <c r="D18" s="2">
         <v>0.54223060607910156</v>
       </c>
       <c r="E18" s="2">
-        <v>0.5078432559967041</v>
+        <v>0.50154757499694824</v>
       </c>
     </row>
     <row r="19">
@@ -368,13 +368,13 @@
         <v>0.98783475160598755</v>
       </c>
       <c r="C19" s="2">
-        <v>0.96644324064254761</v>
+        <v>0.95704132318496704</v>
       </c>
       <c r="D19" s="2">
         <v>0.58736658096313477</v>
       </c>
       <c r="E19" s="2">
-        <v>0.55823147296905518</v>
+        <v>0.55189222097396851</v>
       </c>
     </row>
     <row r="20">
@@ -385,13 +385,13 @@
         <v>0.86229372024536133</v>
       </c>
       <c r="C20" s="2">
-        <v>0.80186676979064941</v>
+        <v>0.79068160057067871</v>
       </c>
       <c r="D20" s="2">
         <v>0.58975428342819214</v>
       </c>
       <c r="E20" s="2">
-        <v>0.55724692344665527</v>
+        <v>0.55079007148742676</v>
       </c>
     </row>
     <row r="21">
@@ -402,13 +402,13 @@
         <v>0.7834208607673645</v>
       </c>
       <c r="C21" s="2">
-        <v>0.70771795511245728</v>
+        <v>0.69867235422134399</v>
       </c>
       <c r="D21" s="2">
         <v>0.62779784202575684</v>
       </c>
       <c r="E21" s="2">
-        <v>0.59112966060638428</v>
+        <v>0.58355838060379028</v>
       </c>
     </row>
     <row r="22">
@@ -419,13 +419,13 @@
         <v>0.56541162729263306</v>
       </c>
       <c r="C22" s="2">
-        <v>0.50165247917175293</v>
+        <v>0.48842698335647583</v>
       </c>
       <c r="D22" s="2">
         <v>0.67616474628448486</v>
       </c>
       <c r="E22" s="2">
-        <v>0.62921631336212158</v>
+        <v>0.62087398767471313</v>
       </c>
     </row>
     <row r="23">
@@ -436,13 +436,13 @@
         <v>0.92950445413589478</v>
       </c>
       <c r="C23" s="2">
-        <v>0.90704536437988281</v>
+        <v>0.90077316761016846</v>
       </c>
       <c r="D23" s="2">
         <v>0.7726747989654541</v>
       </c>
       <c r="E23" s="2">
-        <v>0.7279888391494751</v>
+        <v>0.71846038103103638</v>
       </c>
     </row>
     <row r="24">
@@ -453,13 +453,13 @@
         <v>0.75843614339828491</v>
       </c>
       <c r="C24" s="2">
-        <v>0.72591394186019897</v>
+        <v>0.71778750419616699</v>
       </c>
       <c r="D24" s="2">
         <v>0.72733175754547119</v>
       </c>
       <c r="E24" s="2">
-        <v>0.6796460747718811</v>
+        <v>0.67040210962295532</v>
       </c>
     </row>
     <row r="25">
@@ -470,13 +470,13 @@
         <v>0.5745013952255249</v>
       </c>
       <c r="C25" s="2">
-        <v>0.50034099817276001</v>
+        <v>0.48806893825531006</v>
       </c>
       <c r="D25" s="2">
         <v>0.64191234111785889</v>
       </c>
       <c r="E25" s="2">
-        <v>0.58127343654632568</v>
+        <v>0.57255035638809204</v>
       </c>
     </row>
     <row r="26">
@@ -487,13 +487,13 @@
         <v>0.60401636362075806</v>
       </c>
       <c r="C26" s="2">
-        <v>0.57252109050750732</v>
+        <v>0.56650310754776001</v>
       </c>
       <c r="D26" s="2">
         <v>0.54834198951721191</v>
       </c>
       <c r="E26" s="2">
-        <v>0.47506833076477051</v>
+        <v>0.46672904491424561</v>
       </c>
     </row>
     <row r="27">
@@ -504,13 +504,13 @@
         <v>0.88865375518798828</v>
       </c>
       <c r="C27" s="2">
-        <v>0.86839777231216431</v>
+        <v>0.85818850994110107</v>
       </c>
       <c r="D27" s="2">
         <v>0.52398020029067993</v>
       </c>
       <c r="E27" s="2">
-        <v>0.44424682855606079</v>
+        <v>0.43698802590370178</v>
       </c>
     </row>
     <row r="28">
@@ -521,13 +521,13 @@
         <v>0.57974767684936523</v>
       </c>
       <c r="C28" s="2">
-        <v>0.53135812282562256</v>
+        <v>0.52451694011688232</v>
       </c>
       <c r="D28" s="2">
         <v>0.44605356454849243</v>
       </c>
       <c r="E28" s="2">
-        <v>0.35953664779663086</v>
+        <v>0.3521135151386261</v>
       </c>
     </row>
     <row r="29">
@@ -538,13 +538,13 @@
         <v>0.093518778681755066</v>
       </c>
       <c r="C29" s="2">
-        <v>-0.083486981689929962</v>
+        <v>-0.089984297752380371</v>
       </c>
       <c r="D29" s="2">
         <v>0.34521672129631042</v>
       </c>
       <c r="E29" s="2">
-        <v>0.24805796146392822</v>
+        <v>0.24135279655456543</v>
       </c>
     </row>
     <row r="30">
@@ -555,13 +555,13 @@
         <v>-0.058712445199489594</v>
       </c>
       <c r="C30" s="2">
-        <v>-0.24812793731689453</v>
+        <v>-0.25371956825256348</v>
       </c>
       <c r="D30" s="2">
         <v>0.27751493453979492</v>
       </c>
       <c r="E30" s="2">
-        <v>0.17702849209308624</v>
+        <v>0.17143714427947998</v>
       </c>
     </row>
     <row r="31">
@@ -572,13 +572,13 @@
         <v>0.34615576267242432</v>
       </c>
       <c r="C31" s="2">
-        <v>0.22425921261310577</v>
+        <v>0.22075805068016052</v>
       </c>
       <c r="D31" s="2">
         <v>0.21286661922931671</v>
       </c>
       <c r="E31" s="2">
-        <v>0.11276738345623016</v>
+        <v>0.10790103673934937</v>
       </c>
     </row>
     <row r="32">
@@ -589,13 +589,13 @@
         <v>0.22816456854343414</v>
       </c>
       <c r="C32" s="2">
-        <v>0.14465358853340149</v>
+        <v>0.13690249621868134</v>
       </c>
       <c r="D32" s="2">
         <v>0.11221088469028473</v>
       </c>
       <c r="E32" s="2">
-        <v>0.0037512965500354767</v>
+        <v>-0.00035711284726858139</v>
       </c>
     </row>
     <row r="33">
@@ -606,13 +606,13 @@
         <v>-0.14909525215625763</v>
       </c>
       <c r="C33" s="2">
-        <v>-0.27739426493644714</v>
+        <v>-0.27905899286270142</v>
       </c>
       <c r="D33" s="2">
         <v>0.029440870508551598</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.080971375107765198</v>
+        <v>-0.08469054102897644</v>
       </c>
     </row>
     <row r="34">
@@ -623,13 +623,13 @@
         <v>-0.034814868122339249</v>
       </c>
       <c r="C34" s="2">
-        <v>-0.13892413675785065</v>
+        <v>-0.14117200672626495</v>
       </c>
       <c r="D34" s="2">
         <v>0.03338068351149559</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.071730323135852814</v>
+        <v>-0.074627459049224854</v>
       </c>
     </row>
     <row r="35">
@@ -640,13 +640,13 @@
         <v>0.022181600332260132</v>
       </c>
       <c r="C35" s="2">
-        <v>-0.0058289356529712677</v>
+        <v>-0.0053218221291899681</v>
       </c>
       <c r="D35" s="2">
         <v>0.025342671200633049</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.083100423216819763</v>
+        <v>-0.085003659129142761</v>
       </c>
     </row>
     <row r="36">
@@ -657,13 +657,13 @@
         <v>-0.017247855663299561</v>
       </c>
       <c r="C36" s="2">
-        <v>-0.11274699866771698</v>
+        <v>-0.11613481491804123</v>
       </c>
       <c r="D36" s="2">
         <v>-0.023631807416677475</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.13116812705993652</v>
+        <v>-0.13279837369918823</v>
       </c>
     </row>
     <row r="37">
@@ -674,13 +674,13 @@
         <v>-0.1651824563741684</v>
       </c>
       <c r="C37" s="2">
-        <v>-0.2311459481716156</v>
+        <v>-0.23448389768600464</v>
       </c>
       <c r="D37" s="2">
         <v>-0.041741345077753067</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.16337338089942932</v>
+        <v>-0.16419225931167603</v>
       </c>
     </row>
     <row r="38">
@@ -691,13 +691,13 @@
         <v>0.12897710502147675</v>
       </c>
       <c r="C38" s="2">
-        <v>-0.00031748833134770393</v>
+        <v>0.00058343965793028474</v>
       </c>
       <c r="D38" s="2">
         <v>-0.0066232206299901009</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.13906648755073547</v>
+        <v>-0.13934282958507538</v>
       </c>
     </row>
     <row r="39">
@@ -708,13 +708,13 @@
         <v>-0.13105456531047821</v>
       </c>
       <c r="C39" s="2">
-        <v>-0.35045883059501648</v>
+        <v>-0.34710535407066345</v>
       </c>
       <c r="D39" s="2">
         <v>0.0067126024514436722</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.13146647810935974</v>
+        <v>-0.1314513236284256</v>
       </c>
     </row>
     <row r="40">
@@ -725,13 +725,13 @@
         <v>-0.09461454302072525</v>
       </c>
       <c r="C40" s="2">
-        <v>-0.20835006237030029</v>
+        <v>-0.20939438045024872</v>
       </c>
       <c r="D40" s="2">
         <v>0.03950674831867218</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.11808700114488602</v>
+        <v>-0.1181572824716568</v>
       </c>
     </row>
     <row r="41">
@@ -742,13 +742,13 @@
         <v>0.065178714692592621</v>
       </c>
       <c r="C41" s="2">
-        <v>-0.14519371092319489</v>
+        <v>-0.14564251899719238</v>
       </c>
       <c r="D41" s="2">
         <v>0.076159395277500153</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.086544610559940338</v>
+        <v>-0.086344771087169647</v>
       </c>
     </row>
     <row r="42">
@@ -759,13 +759,13 @@
         <v>0.16696788370609283</v>
       </c>
       <c r="C42" s="2">
-        <v>-0.058632321655750275</v>
+        <v>-0.055414158850908279</v>
       </c>
       <c r="D42" s="2">
         <v>0.13985089957714081</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.027729466557502747</v>
+        <v>-0.027680300176143646</v>
       </c>
     </row>
     <row r="43">
@@ -776,13 +776,13 @@
         <v>0.085207536816596985</v>
       </c>
       <c r="C43" s="2">
-        <v>-0.070524029433727264</v>
+        <v>-0.070148363709449768</v>
       </c>
       <c r="D43" s="2">
         <v>0.17068886756896973</v>
       </c>
       <c r="E43" s="2">
-        <v>0.0063531943596899509</v>
+        <v>0.0060089309699833393</v>
       </c>
     </row>
     <row r="44">
@@ -793,13 +793,13 @@
         <v>0.31732892990112305</v>
       </c>
       <c r="C44" s="2">
-        <v>0.11458641290664673</v>
+        <v>0.11432453989982605</v>
       </c>
       <c r="D44" s="2">
         <v>0.23953601717948914</v>
       </c>
       <c r="E44" s="2">
-        <v>0.082219205796718597</v>
+        <v>0.080893144011497498</v>
       </c>
     </row>
     <row r="45">
@@ -810,13 +810,13 @@
         <v>0.3126259446144104</v>
       </c>
       <c r="C45" s="2">
-        <v>0.17113450169563293</v>
+        <v>0.17017775774002075</v>
       </c>
       <c r="D45" s="2">
         <v>0.32293534278869629</v>
       </c>
       <c r="E45" s="2">
-        <v>0.16530118882656097</v>
+        <v>0.16324751079082489</v>
       </c>
     </row>
     <row r="46">
@@ -827,13 +827,13 @@
         <v>0.40804114937782288</v>
       </c>
       <c r="C46" s="2">
-        <v>0.29819032549858093</v>
+        <v>0.29349634051322937</v>
       </c>
       <c r="D46" s="2">
         <v>0.37612941861152649</v>
       </c>
       <c r="E46" s="2">
-        <v>0.22521060705184937</v>
+        <v>0.2231232076883316</v>
       </c>
     </row>
     <row r="47">
@@ -844,13 +844,13 @@
         <v>0.40651878714561462</v>
       </c>
       <c r="C47" s="2">
-        <v>0.30642646551132202</v>
+        <v>0.3037865161895752</v>
       </c>
       <c r="D47" s="2">
         <v>0.42497488856315613</v>
       </c>
       <c r="E47" s="2">
-        <v>0.2819570004940033</v>
+        <v>0.27920329570770264</v>
       </c>
     </row>
     <row r="48">
@@ -861,13 +861,13 @@
         <v>0.48856979608535767</v>
       </c>
       <c r="C48" s="2">
-        <v>0.33233526349067688</v>
+        <v>0.32685256004333496</v>
       </c>
       <c r="D48" s="2">
         <v>0.47562271356582642</v>
       </c>
       <c r="E48" s="2">
-        <v>0.32222369313240051</v>
+        <v>0.31907576322555542</v>
       </c>
     </row>
     <row r="49">
@@ -878,13 +878,13 @@
         <v>0.65597927570343018</v>
       </c>
       <c r="C49" s="2">
-        <v>0.53938776254653931</v>
+        <v>0.5317949652671814</v>
       </c>
       <c r="D49" s="2">
         <v>0.50628876686096191</v>
       </c>
       <c r="E49" s="2">
-        <v>0.35612225532531738</v>
+        <v>0.35285100340843201</v>
       </c>
     </row>
     <row r="50">
@@ -895,13 +895,13 @@
         <v>0.54392540454864502</v>
       </c>
       <c r="C50" s="2">
-        <v>0.39399105310440063</v>
+        <v>0.39323875308036804</v>
       </c>
       <c r="D50" s="2">
         <v>0.53772157430648804</v>
       </c>
       <c r="E50" s="2">
-        <v>0.37842926383018494</v>
+        <v>0.37535342574119568</v>
       </c>
     </row>
     <row r="51">
@@ -912,13 +912,13 @@
         <v>0.60657721757888794</v>
       </c>
       <c r="C51" s="2">
-        <v>0.45208531618118286</v>
+        <v>0.44930663704872131</v>
       </c>
       <c r="D51" s="2">
         <v>0.54334825277328491</v>
       </c>
       <c r="E51" s="2">
-        <v>0.37346422672271729</v>
+        <v>0.37028110027313232</v>
       </c>
     </row>
     <row r="52">
@@ -929,13 +929,13 @@
         <v>0.54103797674179077</v>
       </c>
       <c r="C52" s="2">
-        <v>0.2918761670589447</v>
+        <v>0.28870385885238647</v>
       </c>
       <c r="D52" s="2">
         <v>0.58508741855621338</v>
       </c>
       <c r="E52" s="2">
-        <v>0.40517356991767883</v>
+        <v>0.40225690603256226</v>
       </c>
     </row>
     <row r="53">
@@ -946,13 +946,13 @@
         <v>0.5933234691619873</v>
       </c>
       <c r="C53" s="2">
-        <v>0.41967332363128662</v>
+        <v>0.41830155253410339</v>
       </c>
       <c r="D53" s="2">
         <v>0.64761435985565186</v>
       </c>
       <c r="E53" s="2">
-        <v>0.46538490056991577</v>
+        <v>0.46304550766944885</v>
       </c>
     </row>
     <row r="54">
@@ -963,13 +963,13 @@
         <v>0.59552127122879028</v>
       </c>
       <c r="C54" s="2">
-        <v>0.37189778685569763</v>
+        <v>0.37269967794418335</v>
       </c>
       <c r="D54" s="2">
         <v>0.68400126695632935</v>
       </c>
       <c r="E54" s="2">
-        <v>0.50265538692474365</v>
+        <v>0.50115138292312622</v>
       </c>
     </row>
     <row r="55">
@@ -980,13 +980,13 @@
         <v>0.45868101716041565</v>
       </c>
       <c r="C55" s="2">
-        <v>0.25350496172904968</v>
+        <v>0.24784550070762634</v>
       </c>
       <c r="D55" s="2">
         <v>0.70473229885101318</v>
       </c>
       <c r="E55" s="2">
-        <v>0.52199298143386841</v>
+        <v>0.52044379711151123</v>
       </c>
     </row>
     <row r="56">
@@ -997,13 +997,13 @@
         <v>0.78217107057571411</v>
       </c>
       <c r="C56" s="2">
-        <v>0.59181046485900879</v>
+        <v>0.59156876802444458</v>
       </c>
       <c r="D56" s="2">
         <v>0.73539263010025024</v>
       </c>
       <c r="E56" s="2">
-        <v>0.5561710000038147</v>
+        <v>0.55489635467529297</v>
       </c>
     </row>
     <row r="57">
@@ -1014,13 +1014,13 @@
         <v>1.0513128042221069</v>
       </c>
       <c r="C57" s="2">
-        <v>0.87423735857009888</v>
+        <v>0.87394994497299194</v>
       </c>
       <c r="D57" s="2">
         <v>0.75555700063705444</v>
       </c>
       <c r="E57" s="2">
-        <v>0.59127509593963623</v>
+        <v>0.59029644727706909</v>
       </c>
     </row>
     <row r="58">
@@ -1031,13 +1031,13 @@
         <v>0.98346120119094849</v>
       </c>
       <c r="C58" s="2">
-        <v>0.87482202053070068</v>
+        <v>0.87474757432937622</v>
       </c>
       <c r="D58" s="2">
         <v>0.79562336206436157</v>
       </c>
       <c r="E58" s="2">
-        <v>0.62913239002227783</v>
+        <v>0.62854927778244019</v>
       </c>
     </row>
     <row r="59">
@@ -1048,13 +1048,13 @@
         <v>0.73050457239151001</v>
       </c>
       <c r="C59" s="2">
-        <v>0.56802940368652344</v>
+        <v>0.56687039136886597</v>
       </c>
       <c r="D59" s="2">
         <v>0.80862295627593994</v>
       </c>
       <c r="E59" s="2">
-        <v>0.63972145318984985</v>
+        <v>0.63882952928543091</v>
       </c>
     </row>
     <row r="60">
@@ -1065,13 +1065,13 @@
         <v>0.88252043724060059</v>
       </c>
       <c r="C60" s="2">
-        <v>0.75968754291534424</v>
+        <v>0.75938010215759277</v>
       </c>
       <c r="D60" s="2">
         <v>0.83484983444213867</v>
       </c>
       <c r="E60" s="2">
-        <v>0.67448800802230835</v>
+        <v>0.6737520694732666</v>
       </c>
     </row>
     <row r="61">
@@ -1082,13 +1082,13 @@
         <v>0.72251707315444946</v>
       </c>
       <c r="C61" s="2">
-        <v>0.60781276226043701</v>
+        <v>0.60730457305908203</v>
       </c>
       <c r="D61" s="2">
-        <v>0.84143465757369995</v>
+        <v>0.85150361061096191</v>
       </c>
       <c r="E61" s="2">
-        <v>0.684822678565979</v>
+        <v>0.69353616237640381</v>
       </c>
     </row>
     <row r="62">
@@ -1099,13 +1099,13 @@
         <v>0.95392090082168579</v>
       </c>
       <c r="C62" s="2">
-        <v>0.76038902997970581</v>
+        <v>0.76257693767547607</v>
       </c>
       <c r="D62" s="2">
-        <v>0.81145209074020386</v>
+        <v>0.80948507785797119</v>
       </c>
       <c r="E62" s="2">
-        <v>0.65776348114013672</v>
+        <v>0.64453083276748657</v>
       </c>
     </row>
     <row r="63">
@@ -1116,13 +1116,13 @@
         <v>0.71251761913299561</v>
       </c>
       <c r="C63" s="2">
-        <v>0.4671996533870697</v>
+        <v>0.46522194147109985</v>
       </c>
       <c r="D63" s="2">
-        <v>0.7827838659286499</v>
+        <v>0.80086058378219604</v>
       </c>
       <c r="E63" s="2">
-        <v>0.62158703804016113</v>
+        <v>0.62764537334442139</v>
       </c>
     </row>
     <row r="64">
@@ -1133,23 +1133,176 @@
         <v>0.69472277164459229</v>
       </c>
       <c r="C64" s="2">
-        <v>0.56640380620956421</v>
+        <v>0.56214839220046997</v>
       </c>
       <c r="D64" s="2">
-        <v>0.7932397723197937</v>
+        <v>0.80227190256118774</v>
       </c>
       <c r="E64" s="2">
-        <v>0.63229858875274658</v>
+        <v>0.63825440406799316</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1">
         <v>45748</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="B65" s="2">
+        <v>0.93205505609512329</v>
+      </c>
+      <c r="C65" s="2">
+        <v>0.76962566375732422</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0.75733822584152222</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.58699607849121094</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.6731458306312561</v>
+      </c>
+      <c r="C66" s="2">
+        <v>0.43290209770202637</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.76732760667800903</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0.59065043926239014</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.9058411717414856</v>
+      </c>
+      <c r="C67" s="2">
+        <v>0.72277814149856567</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.74097126722335815</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.57193070650100708</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.74320626258850098</v>
+      </c>
+      <c r="C68" s="2">
+        <v>0.66235184669494629</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.77277737855911255</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.62249237298965454</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.47811752557754517</v>
+      </c>
+      <c r="C69" s="2">
+        <v>0.29805514216423035</v>
+      </c>
+      <c r="D69" s="2">
+        <v>0.78271418809890747</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.63275027275085449</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.81242156028747559</v>
+      </c>
+      <c r="C70" s="2">
+        <v>0.64019381999969482</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.76404654979705811</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.61564087867736816</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.71671366691589355</v>
+      </c>
+      <c r="C71" s="2">
+        <v>0.59409910440444946</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0.77703237533569336</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0.6417464017868042</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.99877250194549561</v>
+      </c>
+      <c r="C72" s="2">
+        <v>0.9202771782875061</v>
+      </c>
+      <c r="D72" s="2">
+        <v>0.75556427240371704</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0.62824112176895142</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.78415399789810181</v>
+      </c>
+      <c r="C73" s="2">
+        <v>0.65446954965591431</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0.75803583860397339</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0.62141895294189453</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
     </row>
   </sheetData>
 </worksheet>
